--- a/docs/quality/Technical Debt Register/Technical Debt Register v0.4.xlsx
+++ b/docs/quality/Technical Debt Register/Technical Debt Register v0.4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elind\m4-wt\records\docs\quality\Technical Debt Register\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D20D457-F75F-411F-8638-464303B06ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41F7C82-5200-47FA-9A36-73BE2FDFD438}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -298,9 +298,6 @@
     <t>Each test was written to check one thing (the Problem.code set, DEF-002; the route set), and no YAML parser is a project dependency.</t>
   </si>
   <si>
-    <t>Known shortcuts and unimplemented baselined rules, why each was accepted, what it costs while unpaid, and what repaying it involves. A debt item is never deleted: a repaid item is marked Repaid with its PR. | Version 0.4 (17/10/2026, E. Lindsay). M4 build (PR #136, frozen at 6408ab7): TD-003, TD-005 and TD-006 marked Repaid; TD-001 marked Partly repaid (the notification subscriber is registered; the reportingCounts projection is not); TD-007 marked Repaid by PR #123 (merged to dev before M4); TD-008 marked Repaid by PR #122, with its evidence the integration job on the dev push after PR #136 (CI run 39079571516 on dev at cb8bca3, 17/10/2026 23:35 UTC: 40 of 40, 0 skipped). TD-002 and TD-004 unchanged. No new item. | Version 0.3 (15/10/2026). Adds TD-005 (AC-FR-1.3: a rejected operation is not recorded), TD-006 (no unit test asserts that a reject without a reason is refused) and TD-007 (the OpenAPI tests do not parse the YAML), raised by E. Lindsay, and TD-008 (the 8 integration cases never run in CI), raised by C. Burger. TD-004 marked Repaid on the test and staging clusters: the provisioning step is built (PR #98) and was run with RESULT PASS 21 of 21 on the test cluster (PR #102) and the staging cluster (PR #111); production has no cluster yet. TD-001 to TD-003 unchanged. Version 0.2 (12/10/2026). Adds TD-003 (the client builds its transition choices from the shared STATUS values rather than being told by the server which transitions the actor may make) and TD-004 (no step builds the database indexes the schemas declare, and the application’s database role cannot), both raised by E. Lindsay; TD-001 and TD-002 unchanged. Version 0.1 (11/10/2026). Register created during M3 Phase 0 with TD-001 (DEC-011 subscribers not registered) and TD-002 (the FR-1.6 role and group union specified in DB-01 §3.7 but not implemented), both raised by E. Lindsay.</t>
-  </si>
-  <si>
     <t>Partly repaid (PR #136, 82f41c4). The NotificationSubscriber is registered in the composition root and creates the requester's notifications (FR-3.4; NV-131, NV-132). The ReportingProjectionSubscriber is still not registered: the management view computes its counts from requests directly (FR-8.1, FR-8.2), so reportingCounts is not maintained, and attaching it still waits on OI-14. Open for the projection.</t>
   </si>
   <si>
@@ -313,12 +310,6 @@
     <t>Repaid (PR #136, 804138f). The FR-6.6 unit test now asserts that a reject without a reason is refused; NV-141 repeats NV-97's break (the reason check removed for Rejected alone) and the test fails.</t>
   </si>
   <si>
-    <t>Repaid (PR #123, 38b055a, merged to dev 7f7f324). The OpenAPI contract tests parse docs/api/openapi.yaml and fail on a parse error or a duplicate key; the negative verification is recorded.</t>
-  </si>
-  <si>
-    <t>Repaid (PR #122): the 8 cases run in CI against a single-node MongoDB 8.0 replica set started in the job, with no cluster credential. On the dev push of PR #136's merge commit cb8bca3 (CI run 39079571516, 17/10/2026 23:35 UTC) the job ran 40 of 40, 0 fail, 0 skipped; PR #122's own run on the earlier dev was 25 of 40, the M3 DEC-015 defects that PR #136 fixes. The job is not yet a required check.</t>
-  </si>
-  <si>
     <t>DEC-011 · OI-14 · DEC-018 · PR #136 (82f41c4) · NV-131 · NV-132</t>
   </si>
   <si>
@@ -334,7 +325,16 @@
     <t>PR #105 · DEF-002 · DEC-015 · PR #123 · docs/evidence/M4-CI/TD-007_openapi_parse_negative_verification.txt</t>
   </si>
   <si>
-    <t>tests/integration/ · docs/quality/M3_API_Test_Specification.md · docs/evidence/M3_API_Test_Run.txt · DEF-007 to DEF-011 · CR-001 · PR #122 · CI run 39079571516 (dev, cb8bca3: 40 of 40) · PR #136</t>
+    <t>Known shortcuts and unimplemented baselined rules, why each was accepted, what it costs while unpaid, and what repaying it involves. A debt item is never deleted: a repaid item is marked Repaid with its PR. | Version 0.4 (17/10/2026, E. Lindsay). M4 build (PR #136, frozen at 6408ab7): TD-003, TD-005 and TD-006 marked Repaid; TD-001 marked Partly repaid (the notification subscriber is registered; the reportingCounts projection is not); TD-007 marked Repaid by PR #123 (C. Burger; merged to dev before M4), and its owner set to C. Burger; TD-008 marked Repaid by PR #122, with its evidence the integration job on the dev push after PR #136 (CI run 39079571516 on dev at cb8bca3, 17/10/2026 23:35 UTC: 40 of 40, 0 skipped), and the job a required check in the dev ruleset ("dev rule", which covers dev and main) since 18/10/2026, set by C. Burger. TD-002 and TD-004 unchanged. No new item. | Version 0.3 (15/10/2026). Adds TD-005 (AC-FR-1.3: a rejected operation is not recorded), TD-006 (no unit test asserts that a reject without a reason is refused) and TD-007 (the OpenAPI tests do not parse the YAML), raised by E. Lindsay, and TD-008 (the 8 integration cases never run in CI), raised by C. Burger. TD-004 marked Repaid on the test and staging clusters: the provisioning step is built (PR #98) and was run with RESULT PASS 21 of 21 on the test cluster (PR #102) and the staging cluster (PR #111); production has no cluster yet. TD-001 to TD-003 unchanged. Version 0.2 (12/10/2026). Adds TD-003 (the client builds its transition choices from the shared STATUS values rather than being told by the server which transitions the actor may make) and TD-004 (no step builds the database indexes the schemas declare, and the application’s database role cannot), both raised by E. Lindsay; TD-001 and TD-002 unchanged. Version 0.1 (11/10/2026). Register created during M3 Phase 0 with TD-001 (DEC-011 subscribers not registered) and TD-002 (the FR-1.6 role and group union specified in DB-01 §3.7 but not implemented), both raised by E. Lindsay.</t>
+  </si>
+  <si>
+    <t>Repaid by PR #123 (C. Burger; 38b055a, merged to dev 7f7f324). The OpenAPI contract tests parse docs/api/openapi.yaml and fail on a parse error or a duplicate key; the negative verification is recorded.</t>
+  </si>
+  <si>
+    <t>Repaid (PR #122): the 8 cases run in CI against a single-node MongoDB 8.0 replica set started in the job, with no cluster credential. On the dev push of PR #136's merge commit cb8bca3 (CI run 39079571516, 17/10/2026 23:35 UTC) the job ran 40 of 40, 0 fail, 0 skipped; PR #122's own run on the earlier dev was 25 of 40, the M3 DEC-015 defects that PR #136 fixes. The job is a required check in the dev ruleset ("dev rule", which covers dev and main) since 18/10/2026, set by C. Burger.</t>
+  </si>
+  <si>
+    <t>tests/integration/ · docs/quality/M3_API_Test_Specification.md · docs/evidence/M3_API_Test_Run.txt · DEF-007 to DEF-011 · CR-001 · PR #122 · CI run 39079571516 (dev, cb8bca3: 40 of 40) · PR #136 · dev ruleset "dev rule" (required check, 18/10/2026)</t>
   </si>
 </sst>
 </file>
@@ -817,7 +817,7 @@
     </row>
     <row r="2" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B2" s="6" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -896,10 +896,10 @@
         <v>21</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="2:13" ht="150" customHeight="1" x14ac:dyDescent="0.3">
@@ -974,10 +974,10 @@
         <v>21</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="2:13" ht="409.6" x14ac:dyDescent="0.3">
@@ -1052,10 +1052,10 @@
         <v>46</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="2:13" ht="237.6" x14ac:dyDescent="0.3">
@@ -1091,13 +1091,13 @@
         <v>46</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
-    <row r="11" spans="2:13" ht="237.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:13" ht="250.8" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>52</v>
       </c>
@@ -1127,13 +1127,13 @@
         <v>73</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="2:13" ht="409.6" x14ac:dyDescent="0.3">
@@ -1169,7 +1169,7 @@
         <v>81</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M12" s="5" t="s">
         <v>96</v>
